--- a/data/trans_orig/IP13_R2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R2_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si limitaron su actividad por síntomas en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si en las últimas 2 semanas se han tenido que quedar más de la mitad del día en la cama por síntomas en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1550</t>
+          <t>1455</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8047</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2130</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4832</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>14692</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109233</t>
+          <t>110003</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>115730</t>
+          <t>115825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -883,7 +883,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137559</t>
+          <t>137773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>242658</t>
+          <t>242277</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>252137</t>
+          <t>252301</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4514</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>14595</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18088</t>
+          <t>18368</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13736</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28521</t>
+          <t>27614</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176774</t>
+          <t>175917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>185998</t>
+          <t>185601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236947</t>
+          <t>236667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>248207</t>
+          <t>248392</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>417027</t>
+          <t>417934</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>431812</t>
+          <t>432037</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>2986</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11533</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>4507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>9302</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23422</t>
+          <t>22865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>178052</t>
+          <t>177697</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>186656</t>
+          <t>186599</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>171181</t>
+          <t>170366</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180948</t>
+          <t>180779</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>351449</t>
+          <t>352006</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>365130</t>
+          <t>365569</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,52%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4103</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>14557</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19124</t>
+          <t>18953</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13539</t>
+          <t>13158</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28059</t>
+          <t>28881</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>153924</t>
+          <t>153405</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>163859</t>
+          <t>163599</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162114</t>
+          <t>162285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174655</t>
+          <t>174404</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>321142</t>
+          <t>320320</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>335662</t>
+          <t>336043</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,23%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19011</t>
+          <t>18874</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36467</t>
+          <t>35042</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26271</t>
+          <t>27485</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>48516</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51509</t>
+          <t>51166</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77482</t>
+          <t>77859</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>628873</t>
+          <t>630298</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>646329</t>
+          <t>646466</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>713777</t>
+          <t>712732</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>734977</t>
+          <t>733763</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1349106</t>
+          <t>1348729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1375079</t>
+          <t>1375422</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,41%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP13_R2_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP13_R2_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1455</t>
+          <t>2153</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>10902</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4939</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10342</t>
+          <t>8054</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8630</t>
+          <t>8644</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4668</t>
+          <t>4848</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14692</t>
+          <t>14920</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -833,67 +833,67 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>120573</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>114467</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>123216</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,17%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>113590</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>110003</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>115825</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>96,85%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,8%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,76%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>134750</t>
+          <t>117223</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>129347</t>
+          <t>113017</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>137773</t>
+          <t>119411</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>248339</t>
+          <t>237797</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>242277</t>
+          <t>231521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>252301</t>
+          <t>241593</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,03%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125369</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125369</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125369</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139689</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139689</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139689</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>256969</t>
+          <t>246441</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>256969</t>
+          <t>246441</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>256969</t>
+          <t>246441</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>11020</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>6767</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>18394</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,65%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,75%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>8480</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>4911</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14595</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>11263</t>
+          <t>7718</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>4273</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18368</t>
+          <t>12757</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19743</t>
+          <t>18739</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27614</t>
+          <t>27560</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>226186</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>218812</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>230439</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,35%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,15%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>182032</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>175917</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>185601</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>95,55%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,34%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>243772</t>
+          <t>176695</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>236667</t>
+          <t>171656</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>248392</t>
+          <t>180140</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>425805</t>
+          <t>402880</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>417934</t>
+          <t>394059</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>432037</t>
+          <t>408811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,96%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7404</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3645</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12929</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,4%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,68%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6616</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2986</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11888</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8505</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4507</t>
+          <t>3298</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14920</t>
+          <t>12557</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15121</t>
+          <t>14310</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9302</t>
+          <t>8926</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22865</t>
+          <t>21691</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>160937</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>155412</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>164696</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,6%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>92,32%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>182969</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>177697</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>186599</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,51%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,43%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>176781</t>
+          <t>149298</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170366</t>
+          <t>143647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>180779</t>
+          <t>152906</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>359750</t>
+          <t>310235</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>352006</t>
+          <t>302854</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>365569</t>
+          <t>315619</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,25%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11014</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6615</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17760</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,91%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,49%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>8071</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4363</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14557</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,67%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11845</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18953</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19916</t>
+          <t>18781</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13158</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28881</t>
+          <t>26911</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>158362</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>151616</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>162761</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,5%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>89,51%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,09%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>159891</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>153405</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>163599</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,33%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>169393</t>
+          <t>159378</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>162285</t>
+          <t>153078</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>174404</t>
+          <t>162896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>329285</t>
+          <t>317740</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>320320</t>
+          <t>309610</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>336043</t>
+          <t>323468</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>34234</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>26014</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44933</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,42%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>26858</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18874</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35042</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,04%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,84%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,27%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36553</t>
+          <t>26239</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27485</t>
+          <t>18945</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48516</t>
+          <t>35016</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>63411</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51166</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77859</t>
+          <t>74402</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>666059</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>655360</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>674279</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>900</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>638482</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>630298</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>646466</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>95,96%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,73%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,16%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>926</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>724695</t>
+          <t>602594</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>712732</t>
+          <t>593817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>733763</t>
+          <t>609888</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1363177</t>
+          <t>1268652</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1348729</t>
+          <t>1254723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1375422</t>
+          <t>1279694</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,28%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700293</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761248</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426588</t>
+          <t>1329125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
